--- a/report_forms/043_crash_risk_analysis_form--report_forms.xlsx
+++ b/report_forms/043_crash_risk_analysis_form--report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -642,8 +642,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -671,12 +671,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'name',_'label':_'name',_'hint':_none,_'type':_'text',_'options':_[]}</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'name', 'label': 'name', 'hint': None, 'type': 'text', 'options': []}</t>
+          <t>name</t>
         </is>
       </c>
     </row>
@@ -688,12 +688,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'phone',_'label':_'phone',_'hint':_none,_'type':_'text',_'options':_[]}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'phone', 'label': 'phone', 'hint': None, 'type': 'text', 'options': []}</t>
+          <t>phone</t>
         </is>
       </c>
     </row>
@@ -705,12 +705,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'crash_type',_'label':_'crash_type',_'hint':_none,_'type':_'select_one',_'options':_[{'id':_1,_'name':_'rear_end_collision',_'label':_'rear_end_collision',_'hint':_none,_'type':_'text',_'options':_[]},_{'id':_2,_'name':_'angle_collision',_'label':_'angle_collision',_'hint':_none,_'type':_'text',_'options':_[]},_{'id':_3,_'name':_'pedestrian_collision',_'label':_'pedestrian_collision',_'hint':_none,_'type':_'text',_'options':_[]}]}</t>
+          <t>crash_type</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'crash_type', 'label': 'crash_type', 'hint': None, 'type': 'select_one', 'options': [{'id': 1, 'name': 'rear_end_collision', 'label': 'rear end collision', 'hint': None, 'type': 'text', 'options': []}, {'id': 2, 'name': 'angle_collision', 'label': 'angle collision', 'hint': None, 'type': 'text', 'options': []}, {'id': 3, 'name': 'pedestrian_collision', 'label': 'pedestrian collision', 'hint': None, 'type': 'text', 'options': []}]}</t>
+          <t>crash type</t>
         </is>
       </c>
     </row>
@@ -722,12 +722,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'severity',_'label':_'severity',_'hint':_none,_'type':_'select_one',_'options':_[{'id':_1,_'name':_'not_serious',_'label':_'not_serious',_'hint':_none,_'type':_'text',_'options':_[]},_{'id':_2,_'name':_'serious',_'label':_'serious',_'hint':_none,_'type':_'text',_'options':_[]},_{'id':_3,_'name':_'critical',_'label':_'critical',_'hint':_none,_'type':_'text',_'options':_[]}]}</t>
+          <t>severity</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'severity', 'label': 'severity', 'hint': None, 'type': 'select_one', 'options': [{'id': 1, 'name': 'not_serious', 'label': 'not serious', 'hint': None, 'type': 'text', 'options': []}, {'id': 2, 'name': 'serious', 'label': 'serious', 'hint': None, 'type': 'text', 'options': []}, {'id': 3, 'name': 'critical', 'label': 'critical', 'hint': None, 'type': 'text', 'options': []}]}</t>
+          <t>severity</t>
         </is>
       </c>
     </row>
